--- a/22-10-2026/PAT_Berth_Window.xlsx
+++ b/22-10-2026/PAT_Berth_Window.xlsx
@@ -176,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -270,6 +270,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -733,13 +742,13 @@
       <c r="C4" s="23" t="n">
         <v>537</v>
       </c>
-      <c r="D4" s="40" t="n">
+      <c r="D4" s="43" t="n">
         <v>46316.83333333334</v>
       </c>
-      <c r="E4" s="40" t="n">
+      <c r="E4" s="43" t="n">
         <v>46317.54166666666</v>
       </c>
-      <c r="F4" s="40" t="n">
+      <c r="F4" s="43" t="n">
         <v>46318.66666666666</v>
       </c>
       <c r="G4" s="24">
@@ -771,13 +780,13 @@
       <c r="C5" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D5" s="40" t="n">
+      <c r="D5" s="43" t="n">
         <v>46317.54166666666</v>
       </c>
-      <c r="E5" s="40" t="n">
+      <c r="E5" s="43" t="n">
         <v>46318.58333333334</v>
       </c>
-      <c r="F5" s="40" t="n">
+      <c r="F5" s="43" t="n">
         <v>46320.08333333334</v>
       </c>
       <c r="G5" s="24">
@@ -809,13 +818,13 @@
       <c r="C6" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="43" t="n">
         <v>46320.20833333334</v>
       </c>
-      <c r="E6" s="40" t="n">
+      <c r="E6" s="43" t="n">
         <v>46320.625</v>
       </c>
-      <c r="F6" s="40" t="n">
+      <c r="F6" s="43" t="n">
         <v>46292.125</v>
       </c>
       <c r="G6" s="24">
@@ -847,13 +856,13 @@
       <c r="C7" s="23" t="n">
         <v>482</v>
       </c>
-      <c r="D7" s="40" t="n">
+      <c r="D7" s="43" t="n">
         <v>46316.66666666666</v>
       </c>
-      <c r="E7" s="40" t="n">
+      <c r="E7" s="43" t="n">
         <v>46317.58333333334</v>
       </c>
-      <c r="F7" s="40" t="n">
+      <c r="F7" s="43" t="n">
         <v>46318.54166666666</v>
       </c>
       <c r="G7" s="24">
@@ -885,13 +894,13 @@
       <c r="C8" s="23" t="n">
         <v>548</v>
       </c>
-      <c r="D8" s="40" t="n">
+      <c r="D8" s="43" t="n">
         <v>46317.66666666666</v>
       </c>
-      <c r="E8" s="40" t="n">
+      <c r="E8" s="43" t="n">
         <v>46318.54166666666</v>
       </c>
-      <c r="F8" s="40" t="n">
+      <c r="F8" s="43" t="n">
         <v>46320</v>
       </c>
       <c r="G8" s="24">
@@ -923,13 +932,13 @@
       <c r="C9" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D9" s="40" t="n">
+      <c r="D9" s="43" t="n">
         <v>46320</v>
       </c>
-      <c r="E9" s="40" t="n">
+      <c r="E9" s="43" t="n">
         <v>46320.16666666666</v>
       </c>
-      <c r="F9" s="40" t="n">
+      <c r="F9" s="43" t="n">
         <v>46321.125</v>
       </c>
       <c r="G9" s="24">
@@ -961,13 +970,13 @@
       <c r="C10" s="23" t="n">
         <v>561</v>
       </c>
-      <c r="D10" s="40" t="n">
+      <c r="D10" s="43" t="n">
         <v>46321.58333333334</v>
       </c>
-      <c r="E10" s="40" t="n">
+      <c r="E10" s="43" t="n">
         <v>46321.58333333334</v>
       </c>
-      <c r="F10" s="40" t="n">
+      <c r="F10" s="43" t="n">
         <v>46293.125</v>
       </c>
       <c r="G10" s="24">
@@ -999,13 +1008,13 @@
       <c r="C11" s="23" t="n">
         <v>558</v>
       </c>
-      <c r="D11" s="40" t="n">
+      <c r="D11" s="43" t="n">
         <v>46316.45833333334</v>
       </c>
-      <c r="E11" s="40" t="n">
+      <c r="E11" s="43" t="n">
         <v>46316.5</v>
       </c>
-      <c r="F11" s="40" t="n">
+      <c r="F11" s="43" t="n">
         <v>46318.5</v>
       </c>
       <c r="G11" s="24">
@@ -1037,13 +1046,13 @@
       <c r="C12" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D12" s="40" t="n">
+      <c r="D12" s="43" t="n">
         <v>46318.04166666666</v>
       </c>
-      <c r="E12" s="40" t="n">
+      <c r="E12" s="43" t="n">
         <v>46318.5</v>
       </c>
-      <c r="F12" s="40" t="n">
+      <c r="F12" s="43" t="n">
         <v>46319.625</v>
       </c>
       <c r="G12" s="24">
@@ -1075,13 +1084,13 @@
       <c r="C13" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D13" s="40" t="n">
+      <c r="D13" s="43" t="n">
         <v>46318.91666666666</v>
       </c>
-      <c r="E13" s="40" t="n">
+      <c r="E13" s="43" t="n">
         <v>46319.625</v>
       </c>
-      <c r="F13" s="40" t="n">
+      <c r="F13" s="43" t="n">
         <v>46321.125</v>
       </c>
       <c r="G13" s="24">
@@ -1113,13 +1122,13 @@
       <c r="C14" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D14" s="40" t="n">
+      <c r="D14" s="43" t="n">
         <v>46320.08333333334</v>
       </c>
-      <c r="E14" s="40" t="n">
+      <c r="E14" s="43" t="n">
         <v>46320.16666666666</v>
       </c>
-      <c r="F14" s="40" t="n">
+      <c r="F14" s="43" t="n">
         <v>46321.5</v>
       </c>
       <c r="G14" s="24">
@@ -1151,13 +1160,13 @@
       <c r="C15" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D15" s="40" t="n">
+      <c r="D15" s="43" t="n">
         <v>46317.04166666666</v>
       </c>
-      <c r="E15" s="40" t="n">
+      <c r="E15" s="43" t="n">
         <v>46317.54166666666</v>
       </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="43" t="n">
         <v>46319.04166666666</v>
       </c>
       <c r="G15" s="24">
@@ -1189,13 +1198,13 @@
       <c r="C16" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D16" s="40" t="n">
+      <c r="D16" s="43" t="n">
         <v>46318.25</v>
       </c>
-      <c r="E16" s="40" t="n">
+      <c r="E16" s="43" t="n">
         <v>46319.125</v>
       </c>
-      <c r="F16" s="40" t="n">
+      <c r="F16" s="43" t="n">
         <v>46320.04166666666</v>
       </c>
       <c r="G16" s="24">
@@ -1227,13 +1236,13 @@
       <c r="C17" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D17" s="40" t="n">
+      <c r="D17" s="43" t="n">
         <v>46320.91666666666</v>
       </c>
-      <c r="E17" s="40" t="n">
+      <c r="E17" s="43" t="n">
         <v>46321.25</v>
       </c>
-      <c r="F17" s="40" t="n">
+      <c r="F17" s="43" t="n">
         <v>46292.58333333334</v>
       </c>
       <c r="G17" s="24">
@@ -1265,13 +1274,13 @@
       <c r="C18" s="23" t="n">
         <v>458</v>
       </c>
-      <c r="D18" s="40" t="n">
+      <c r="D18" s="43" t="n">
         <v>46315.75</v>
       </c>
-      <c r="E18" s="40" t="n">
+      <c r="E18" s="43" t="n">
         <v>46317.41666666666</v>
       </c>
-      <c r="F18" s="40" t="n">
+      <c r="F18" s="43" t="n">
         <v>46318.375</v>
       </c>
       <c r="G18" s="24">
@@ -1303,13 +1312,13 @@
       <c r="C19" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D19" s="40" t="n">
+      <c r="D19" s="43" t="n">
         <v>46318.375</v>
       </c>
-      <c r="E19" s="40" t="n">
+      <c r="E19" s="43" t="n">
         <v>46318.375</v>
       </c>
-      <c r="F19" s="40" t="n">
+      <c r="F19" s="43" t="n">
         <v>46319.58333333334</v>
       </c>
       <c r="G19" s="24">
@@ -1341,13 +1350,13 @@
       <c r="C20" s="23" t="n">
         <v>564</v>
       </c>
-      <c r="D20" s="40" t="n">
+      <c r="D20" s="43" t="n">
         <v>46320.41666666666</v>
       </c>
-      <c r="E20" s="40" t="n">
+      <c r="E20" s="43" t="n">
         <v>46320.54166666666</v>
       </c>
-      <c r="F20" s="40" t="n">
+      <c r="F20" s="43" t="n">
         <v>46321.5</v>
       </c>
       <c r="G20" s="24">
@@ -1379,13 +1388,13 @@
       <c r="C21" s="23" t="n">
         <v>565</v>
       </c>
-      <c r="D21" s="40" t="n">
+      <c r="D21" s="43" t="n">
         <v>46317.29166666666</v>
       </c>
-      <c r="E21" s="40" t="n">
+      <c r="E21" s="43" t="n">
         <v>46317.66666666666</v>
       </c>
-      <c r="F21" s="40" t="n">
+      <c r="F21" s="43" t="n">
         <v>46318.375</v>
       </c>
       <c r="G21" s="24">
@@ -1404,7 +1413,7 @@
       <c r="J21" s="23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="A24" s="37" t="inlineStr">
         <is>
           <t>Berth &amp; gate notices on this sheet</t>
         </is>
@@ -1437,13 +1446,13 @@
           <t>Notice / change vs previous sheet</t>
         </is>
       </c>
-      <c r="G25" s="35" t="n"/>
-      <c r="H25" s="35" t="n"/>
-      <c r="I25" s="35" t="n"/>
-      <c r="J25" s="36" t="n"/>
+      <c r="G25" s="38" t="n"/>
+      <c r="H25" s="38" t="n"/>
+      <c r="I25" s="38" t="n"/>
+      <c r="J25" s="39" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr">
+      <c r="A26" s="42" t="inlineStr">
         <is>
           <t>No notices on this sheet</t>
         </is>
